--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333823</v>
+        <v>123333804</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519345</v>
+        <v>519267</v>
       </c>
       <c r="R2" t="n">
-        <v>7003129</v>
+        <v>7003104</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333804</v>
+        <v>123333817</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519267</v>
+        <v>519229</v>
       </c>
       <c r="R3" t="n">
-        <v>7003104</v>
+        <v>7003181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333818</v>
+        <v>123333827</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519316</v>
+        <v>519272</v>
       </c>
       <c r="R4" t="n">
-        <v>7003189</v>
+        <v>7003098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333799</v>
+        <v>123333824</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519233</v>
+        <v>519360</v>
       </c>
       <c r="R5" t="n">
-        <v>7003190</v>
+        <v>7003138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333824</v>
+        <v>123333803</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519360</v>
+        <v>519276</v>
       </c>
       <c r="R6" t="n">
-        <v>7003138</v>
+        <v>7003096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333822</v>
+        <v>123333832</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519337</v>
+        <v>519246</v>
       </c>
       <c r="R7" t="n">
-        <v>7003139</v>
+        <v>7003145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333803</v>
+        <v>123333822</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519276</v>
+        <v>519337</v>
       </c>
       <c r="R8" t="n">
-        <v>7003096</v>
+        <v>7003139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333819</v>
+        <v>123333823</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519202</v>
+        <v>519345</v>
       </c>
       <c r="R9" t="n">
-        <v>7003229</v>
+        <v>7003129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333832</v>
+        <v>123333801</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519246</v>
+        <v>519296</v>
       </c>
       <c r="R10" t="n">
-        <v>7003145</v>
+        <v>7003116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333801</v>
+        <v>123333806</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519296</v>
+        <v>519245</v>
       </c>
       <c r="R11" t="n">
-        <v>7003116</v>
+        <v>7003107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333806</v>
+        <v>123333831</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519245</v>
+        <v>519255</v>
       </c>
       <c r="R12" t="n">
-        <v>7003107</v>
+        <v>7003173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333805</v>
+        <v>123333800</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519254</v>
+        <v>519340</v>
       </c>
       <c r="R13" t="n">
-        <v>7003096</v>
+        <v>7003134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333825</v>
+        <v>123333798</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519351</v>
+        <v>519233</v>
       </c>
       <c r="R14" t="n">
-        <v>7003097</v>
+        <v>7003181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mycket rikligt på sälg</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333817</v>
+        <v>123333799</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519229</v>
+        <v>519233</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003190</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333800</v>
+        <v>123333818</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519340</v>
+        <v>519316</v>
       </c>
       <c r="R16" t="n">
-        <v>7003134</v>
+        <v>7003189</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333826</v>
+        <v>123333819</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519347</v>
+        <v>519202</v>
       </c>
       <c r="R17" t="n">
-        <v>7003094</v>
+        <v>7003229</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
         <v>123333821</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333831</v>
+        <v>123333826</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519255</v>
+        <v>519347</v>
       </c>
       <c r="R19" t="n">
-        <v>7003173</v>
+        <v>7003094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,11 +2530,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333798</v>
+        <v>123333805</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519233</v>
+        <v>519254</v>
       </c>
       <c r="R20" t="n">
-        <v>7003181</v>
+        <v>7003096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,7 +2636,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333827</v>
+        <v>123333825</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519272</v>
+        <v>519351</v>
       </c>
       <c r="R21" t="n">
-        <v>7003098</v>
+        <v>7003097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333804</v>
+        <v>123333826</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519267</v>
+        <v>519347</v>
       </c>
       <c r="R2" t="n">
-        <v>7003104</v>
+        <v>7003094</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333817</v>
+        <v>123333800</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519229</v>
+        <v>519340</v>
       </c>
       <c r="R3" t="n">
-        <v>7003181</v>
+        <v>7003134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333827</v>
+        <v>123333803</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519272</v>
+        <v>519276</v>
       </c>
       <c r="R4" t="n">
-        <v>7003098</v>
+        <v>7003096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333824</v>
+        <v>123333832</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519360</v>
+        <v>519246</v>
       </c>
       <c r="R5" t="n">
-        <v>7003138</v>
+        <v>7003145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333803</v>
+        <v>123333801</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519276</v>
+        <v>519296</v>
       </c>
       <c r="R6" t="n">
-        <v>7003096</v>
+        <v>7003116</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333832</v>
+        <v>123333804</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519246</v>
+        <v>519267</v>
       </c>
       <c r="R7" t="n">
-        <v>7003145</v>
+        <v>7003104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333822</v>
+        <v>123333831</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519337</v>
+        <v>519255</v>
       </c>
       <c r="R8" t="n">
-        <v>7003139</v>
+        <v>7003173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333823</v>
+        <v>123333824</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519345</v>
+        <v>519360</v>
       </c>
       <c r="R9" t="n">
-        <v>7003129</v>
+        <v>7003138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333801</v>
+        <v>123333799</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1546,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519296</v>
+        <v>519233</v>
       </c>
       <c r="R10" t="n">
-        <v>7003116</v>
+        <v>7003190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333806</v>
+        <v>123333822</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519245</v>
+        <v>519337</v>
       </c>
       <c r="R11" t="n">
-        <v>7003107</v>
+        <v>7003139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333831</v>
+        <v>123333819</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519255</v>
+        <v>519202</v>
       </c>
       <c r="R12" t="n">
-        <v>7003173</v>
+        <v>7003229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333800</v>
+        <v>123333825</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519340</v>
+        <v>519351</v>
       </c>
       <c r="R13" t="n">
-        <v>7003134</v>
+        <v>7003097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333798</v>
+        <v>123333805</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519233</v>
+        <v>519254</v>
       </c>
       <c r="R14" t="n">
-        <v>7003181</v>
+        <v>7003096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333799</v>
+        <v>123333806</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519233</v>
+        <v>519245</v>
       </c>
       <c r="R15" t="n">
-        <v>7003190</v>
+        <v>7003107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333818</v>
+        <v>123333821</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519316</v>
+        <v>519369</v>
       </c>
       <c r="R16" t="n">
-        <v>7003189</v>
+        <v>7003165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333819</v>
+        <v>123333823</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519202</v>
+        <v>519345</v>
       </c>
       <c r="R17" t="n">
-        <v>7003229</v>
+        <v>7003129</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333821</v>
+        <v>123333818</v>
       </c>
       <c r="B18" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519369</v>
+        <v>519316</v>
       </c>
       <c r="R18" t="n">
-        <v>7003165</v>
+        <v>7003189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333826</v>
+        <v>123333827</v>
       </c>
       <c r="B19" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519347</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7003094</v>
+        <v>7003098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333805</v>
+        <v>123333817</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519254</v>
+        <v>519229</v>
       </c>
       <c r="R20" t="n">
-        <v>7003096</v>
+        <v>7003181</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,11 +2637,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333825</v>
+        <v>123333798</v>
       </c>
       <c r="B21" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519351</v>
+        <v>519233</v>
       </c>
       <c r="R21" t="n">
-        <v>7003097</v>
+        <v>7003181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mycket rikligt på sälg</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123333826</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333800</v>
+        <v>123333801</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519340</v>
+        <v>519296</v>
       </c>
       <c r="R3" t="n">
-        <v>7003134</v>
+        <v>7003116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333803</v>
+        <v>123333798</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519276</v>
+        <v>519233</v>
       </c>
       <c r="R4" t="n">
-        <v>7003096</v>
+        <v>7003181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333832</v>
+        <v>123333818</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519246</v>
+        <v>519316</v>
       </c>
       <c r="R5" t="n">
-        <v>7003145</v>
+        <v>7003189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333801</v>
+        <v>123333823</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519296</v>
+        <v>519345</v>
       </c>
       <c r="R6" t="n">
-        <v>7003116</v>
+        <v>7003129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333804</v>
+        <v>123333824</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519267</v>
+        <v>519360</v>
       </c>
       <c r="R7" t="n">
-        <v>7003104</v>
+        <v>7003138</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333831</v>
+        <v>123333804</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519255</v>
+        <v>519267</v>
       </c>
       <c r="R8" t="n">
-        <v>7003173</v>
+        <v>7003104</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333824</v>
+        <v>123333821</v>
       </c>
       <c r="B9" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519360</v>
+        <v>519369</v>
       </c>
       <c r="R9" t="n">
-        <v>7003138</v>
+        <v>7003165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333799</v>
+        <v>123333831</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519233</v>
+        <v>519255</v>
       </c>
       <c r="R10" t="n">
-        <v>7003190</v>
+        <v>7003173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333822</v>
+        <v>123333817</v>
       </c>
       <c r="B11" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519337</v>
+        <v>519229</v>
       </c>
       <c r="R11" t="n">
-        <v>7003139</v>
+        <v>7003181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333819</v>
+        <v>123333799</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519202</v>
+        <v>519233</v>
       </c>
       <c r="R12" t="n">
-        <v>7003229</v>
+        <v>7003190</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333825</v>
+        <v>123333822</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519351</v>
+        <v>519337</v>
       </c>
       <c r="R13" t="n">
-        <v>7003097</v>
+        <v>7003139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333805</v>
+        <v>123333832</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519254</v>
+        <v>519246</v>
       </c>
       <c r="R14" t="n">
-        <v>7003096</v>
+        <v>7003145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333806</v>
+        <v>123333800</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2086,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519245</v>
+        <v>519340</v>
       </c>
       <c r="R15" t="n">
-        <v>7003107</v>
+        <v>7003134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333821</v>
+        <v>123333806</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519369</v>
+        <v>519245</v>
       </c>
       <c r="R16" t="n">
-        <v>7003165</v>
+        <v>7003107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333823</v>
+        <v>123333819</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519345</v>
+        <v>519202</v>
       </c>
       <c r="R17" t="n">
-        <v>7003129</v>
+        <v>7003229</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333818</v>
+        <v>123333805</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519316</v>
+        <v>519254</v>
       </c>
       <c r="R18" t="n">
-        <v>7003189</v>
+        <v>7003096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,6 +2423,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333827</v>
+        <v>123333803</v>
       </c>
       <c r="B19" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519276</v>
       </c>
       <c r="R19" t="n">
-        <v>7003098</v>
+        <v>7003096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2530,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333817</v>
+        <v>123333825</v>
       </c>
       <c r="B20" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519229</v>
+        <v>519351</v>
       </c>
       <c r="R20" t="n">
-        <v>7003181</v>
+        <v>7003097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2637,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333798</v>
+        <v>123333827</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519233</v>
+        <v>519272</v>
       </c>
       <c r="R21" t="n">
-        <v>7003181</v>
+        <v>7003098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333803</v>
+        <v>123333819</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519276</v>
+        <v>519202</v>
       </c>
       <c r="R2" t="n">
-        <v>7003096</v>
+        <v>7003229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333822</v>
+        <v>123333831</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519337</v>
+        <v>519255</v>
       </c>
       <c r="R3" t="n">
-        <v>7003139</v>
+        <v>7003173</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333827</v>
+        <v>123333800</v>
       </c>
       <c r="B4" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519272</v>
+        <v>519340</v>
       </c>
       <c r="R4" t="n">
-        <v>7003098</v>
+        <v>7003134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333799</v>
+        <v>123333805</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519233</v>
+        <v>519254</v>
       </c>
       <c r="R5" t="n">
-        <v>7003190</v>
+        <v>7003096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333819</v>
+        <v>123333823</v>
       </c>
       <c r="B6" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519202</v>
+        <v>519345</v>
       </c>
       <c r="R6" t="n">
-        <v>7003229</v>
+        <v>7003129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333798</v>
+        <v>123333832</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519233</v>
+        <v>519246</v>
       </c>
       <c r="R7" t="n">
-        <v>7003181</v>
+        <v>7003145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333804</v>
+        <v>123333821</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519267</v>
+        <v>519369</v>
       </c>
       <c r="R8" t="n">
-        <v>7003104</v>
+        <v>7003165</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333825</v>
+        <v>123333798</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519351</v>
+        <v>519233</v>
       </c>
       <c r="R9" t="n">
-        <v>7003097</v>
+        <v>7003181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt på sälg</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333831</v>
+        <v>123333801</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519255</v>
+        <v>519296</v>
       </c>
       <c r="R10" t="n">
-        <v>7003173</v>
+        <v>7003116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333826</v>
+        <v>123333824</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519347</v>
+        <v>519360</v>
       </c>
       <c r="R11" t="n">
-        <v>7003094</v>
+        <v>7003138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333806</v>
+        <v>123333826</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519245</v>
+        <v>519347</v>
       </c>
       <c r="R12" t="n">
-        <v>7003107</v>
+        <v>7003094</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333823</v>
+        <v>123333822</v>
       </c>
       <c r="B13" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519345</v>
+        <v>519337</v>
       </c>
       <c r="R13" t="n">
-        <v>7003129</v>
+        <v>7003139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333832</v>
+        <v>123333818</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519246</v>
+        <v>519316</v>
       </c>
       <c r="R14" t="n">
-        <v>7003145</v>
+        <v>7003189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333821</v>
+        <v>123333817</v>
       </c>
       <c r="B15" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519369</v>
+        <v>519229</v>
       </c>
       <c r="R15" t="n">
-        <v>7003165</v>
+        <v>7003181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333801</v>
+        <v>123333803</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519296</v>
+        <v>519276</v>
       </c>
       <c r="R16" t="n">
-        <v>7003116</v>
+        <v>7003096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333800</v>
+        <v>123333825</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519340</v>
+        <v>519351</v>
       </c>
       <c r="R17" t="n">
-        <v>7003134</v>
+        <v>7003097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333824</v>
+        <v>123333806</v>
       </c>
       <c r="B18" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519360</v>
+        <v>519245</v>
       </c>
       <c r="R18" t="n">
-        <v>7003138</v>
+        <v>7003107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,6 +2423,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333818</v>
+        <v>123333827</v>
       </c>
       <c r="B19" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519316</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7003189</v>
+        <v>7003098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333805</v>
+        <v>123333804</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519254</v>
+        <v>519267</v>
       </c>
       <c r="R20" t="n">
-        <v>7003096</v>
+        <v>7003104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333817</v>
+        <v>123333799</v>
       </c>
       <c r="B21" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519229</v>
+        <v>519233</v>
       </c>
       <c r="R21" t="n">
-        <v>7003181</v>
+        <v>7003190</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333818</v>
+        <v>123333817</v>
       </c>
       <c r="B14" t="n">
         <v>79862</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519316</v>
+        <v>519229</v>
       </c>
       <c r="R14" t="n">
-        <v>7003189</v>
+        <v>7003181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333817</v>
+        <v>123333818</v>
       </c>
       <c r="B15" t="n">
         <v>79862</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519229</v>
+        <v>519316</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333817</v>
+        <v>123333818</v>
       </c>
       <c r="B14" t="n">
         <v>79862</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519229</v>
+        <v>519316</v>
       </c>
       <c r="R14" t="n">
-        <v>7003181</v>
+        <v>7003189</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333818</v>
+        <v>123333817</v>
       </c>
       <c r="B15" t="n">
         <v>79862</v>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519316</v>
+        <v>519229</v>
       </c>
       <c r="R15" t="n">
-        <v>7003189</v>
+        <v>7003181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123333819</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333831</v>
+        <v>123333803</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519255</v>
+        <v>519276</v>
       </c>
       <c r="R3" t="n">
-        <v>7003173</v>
+        <v>7003096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333800</v>
+        <v>123333823</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519340</v>
+        <v>519345</v>
       </c>
       <c r="R4" t="n">
-        <v>7003134</v>
+        <v>7003129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333805</v>
+        <v>123333832</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519254</v>
+        <v>519246</v>
       </c>
       <c r="R5" t="n">
-        <v>7003096</v>
+        <v>7003145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333823</v>
+        <v>123333822</v>
       </c>
       <c r="B6" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519345</v>
+        <v>519337</v>
       </c>
       <c r="R6" t="n">
-        <v>7003129</v>
+        <v>7003139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333832</v>
+        <v>123333801</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519246</v>
+        <v>519296</v>
       </c>
       <c r="R7" t="n">
-        <v>7003145</v>
+        <v>7003116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333821</v>
+        <v>123333831</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519369</v>
+        <v>519255</v>
       </c>
       <c r="R8" t="n">
-        <v>7003165</v>
+        <v>7003173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333798</v>
+        <v>123333806</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519233</v>
+        <v>519245</v>
       </c>
       <c r="R9" t="n">
-        <v>7003181</v>
+        <v>7003107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333801</v>
+        <v>123333818</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519296</v>
+        <v>519316</v>
       </c>
       <c r="R10" t="n">
-        <v>7003116</v>
+        <v>7003189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333824</v>
+        <v>123333817</v>
       </c>
       <c r="B11" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519360</v>
+        <v>519229</v>
       </c>
       <c r="R11" t="n">
-        <v>7003138</v>
+        <v>7003181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333826</v>
+        <v>123333821</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519347</v>
+        <v>519369</v>
       </c>
       <c r="R12" t="n">
-        <v>7003094</v>
+        <v>7003165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333822</v>
+        <v>123333825</v>
       </c>
       <c r="B13" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519337</v>
+        <v>519351</v>
       </c>
       <c r="R13" t="n">
-        <v>7003139</v>
+        <v>7003097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333818</v>
+        <v>123333824</v>
       </c>
       <c r="B14" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519316</v>
+        <v>519360</v>
       </c>
       <c r="R14" t="n">
-        <v>7003189</v>
+        <v>7003138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333817</v>
+        <v>123333827</v>
       </c>
       <c r="B15" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519229</v>
+        <v>519272</v>
       </c>
       <c r="R15" t="n">
-        <v>7003181</v>
+        <v>7003098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333803</v>
+        <v>123333805</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519276</v>
+        <v>519254</v>
       </c>
       <c r="R16" t="n">
         <v>7003096</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333825</v>
+        <v>123333804</v>
       </c>
       <c r="B17" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519351</v>
+        <v>519267</v>
       </c>
       <c r="R17" t="n">
-        <v>7003097</v>
+        <v>7003104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Mycket rikligt på sälg</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333806</v>
+        <v>123333826</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519245</v>
+        <v>519347</v>
       </c>
       <c r="R18" t="n">
-        <v>7003107</v>
+        <v>7003094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,11 +2423,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333827</v>
+        <v>123333799</v>
       </c>
       <c r="B19" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519233</v>
       </c>
       <c r="R19" t="n">
-        <v>7003098</v>
+        <v>7003190</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,6 +2525,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333804</v>
+        <v>123333800</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519267</v>
+        <v>519340</v>
       </c>
       <c r="R20" t="n">
-        <v>7003104</v>
+        <v>7003134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333799</v>
+        <v>123333798</v>
       </c>
       <c r="B21" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>519233</v>
       </c>
       <c r="R21" t="n">
-        <v>7003190</v>
+        <v>7003181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333819</v>
+        <v>123333831</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519202</v>
+        <v>519255</v>
       </c>
       <c r="R2" t="n">
-        <v>7003229</v>
+        <v>7003173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>123333803</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333823</v>
+        <v>123333819</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519345</v>
+        <v>519202</v>
       </c>
       <c r="R4" t="n">
-        <v>7003129</v>
+        <v>7003229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333832</v>
+        <v>123333824</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519246</v>
+        <v>519360</v>
       </c>
       <c r="R5" t="n">
-        <v>7003145</v>
+        <v>7003138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1096,7 @@
         <v>123333822</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333801</v>
+        <v>123333817</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519296</v>
+        <v>519229</v>
       </c>
       <c r="R7" t="n">
-        <v>7003116</v>
+        <v>7003181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333831</v>
+        <v>123333805</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519255</v>
+        <v>519254</v>
       </c>
       <c r="R8" t="n">
-        <v>7003173</v>
+        <v>7003096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333806</v>
+        <v>123333798</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519245</v>
+        <v>519233</v>
       </c>
       <c r="R9" t="n">
-        <v>7003107</v>
+        <v>7003181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333818</v>
+        <v>123333806</v>
       </c>
       <c r="B10" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519316</v>
+        <v>519245</v>
       </c>
       <c r="R10" t="n">
-        <v>7003189</v>
+        <v>7003107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333817</v>
+        <v>123333825</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519229</v>
+        <v>519351</v>
       </c>
       <c r="R11" t="n">
-        <v>7003181</v>
+        <v>7003097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333821</v>
+        <v>123333800</v>
       </c>
       <c r="B12" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519369</v>
+        <v>519340</v>
       </c>
       <c r="R12" t="n">
-        <v>7003165</v>
+        <v>7003134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333825</v>
+        <v>123333826</v>
       </c>
       <c r="B13" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519351</v>
+        <v>519347</v>
       </c>
       <c r="R13" t="n">
-        <v>7003097</v>
+        <v>7003094</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333824</v>
+        <v>123333799</v>
       </c>
       <c r="B14" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519360</v>
+        <v>519233</v>
       </c>
       <c r="R14" t="n">
-        <v>7003138</v>
+        <v>7003190</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333827</v>
+        <v>123333821</v>
       </c>
       <c r="B15" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519272</v>
+        <v>519369</v>
       </c>
       <c r="R15" t="n">
-        <v>7003098</v>
+        <v>7003165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333805</v>
+        <v>123333827</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519254</v>
+        <v>519272</v>
       </c>
       <c r="R16" t="n">
-        <v>7003096</v>
+        <v>7003098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333804</v>
+        <v>123333832</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519267</v>
+        <v>519246</v>
       </c>
       <c r="R17" t="n">
-        <v>7003104</v>
+        <v>7003145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333826</v>
+        <v>123333823</v>
       </c>
       <c r="B18" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519347</v>
+        <v>519345</v>
       </c>
       <c r="R18" t="n">
-        <v>7003094</v>
+        <v>7003129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333799</v>
+        <v>123333818</v>
       </c>
       <c r="B19" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519233</v>
+        <v>519316</v>
       </c>
       <c r="R19" t="n">
-        <v>7003190</v>
+        <v>7003189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,11 +2530,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333800</v>
+        <v>123333804</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519340</v>
+        <v>519267</v>
       </c>
       <c r="R20" t="n">
-        <v>7003134</v>
+        <v>7003104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333798</v>
+        <v>123333801</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519233</v>
+        <v>519296</v>
       </c>
       <c r="R21" t="n">
-        <v>7003181</v>
+        <v>7003116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333831</v>
+        <v>123333801</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519255</v>
+        <v>519296</v>
       </c>
       <c r="R2" t="n">
-        <v>7003173</v>
+        <v>7003116</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333803</v>
+        <v>123333824</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519276</v>
+        <v>519360</v>
       </c>
       <c r="R3" t="n">
-        <v>7003096</v>
+        <v>7003138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333819</v>
+        <v>123333823</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519202</v>
+        <v>519345</v>
       </c>
       <c r="R4" t="n">
-        <v>7003229</v>
+        <v>7003129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333824</v>
+        <v>123333818</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519360</v>
+        <v>519316</v>
       </c>
       <c r="R5" t="n">
-        <v>7003138</v>
+        <v>7003189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333822</v>
+        <v>123333799</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519337</v>
+        <v>519233</v>
       </c>
       <c r="R6" t="n">
-        <v>7003139</v>
+        <v>7003190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333817</v>
+        <v>123333832</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519229</v>
+        <v>519246</v>
       </c>
       <c r="R7" t="n">
-        <v>7003181</v>
+        <v>7003145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333798</v>
+        <v>123333800</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519233</v>
+        <v>519340</v>
       </c>
       <c r="R9" t="n">
-        <v>7003181</v>
+        <v>7003134</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333806</v>
+        <v>123333817</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519245</v>
+        <v>519229</v>
       </c>
       <c r="R10" t="n">
-        <v>7003107</v>
+        <v>7003181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333825</v>
+        <v>123333821</v>
       </c>
       <c r="B11" t="n">
         <v>79869</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519351</v>
+        <v>519369</v>
       </c>
       <c r="R11" t="n">
-        <v>7003097</v>
+        <v>7003165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333800</v>
+        <v>123333806</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519340</v>
+        <v>519245</v>
       </c>
       <c r="R12" t="n">
-        <v>7003134</v>
+        <v>7003107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333826</v>
+        <v>123333804</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519347</v>
+        <v>519267</v>
       </c>
       <c r="R13" t="n">
-        <v>7003094</v>
+        <v>7003104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333799</v>
+        <v>123333827</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519233</v>
+        <v>519272</v>
       </c>
       <c r="R14" t="n">
-        <v>7003190</v>
+        <v>7003098</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333821</v>
+        <v>123333831</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519369</v>
+        <v>519255</v>
       </c>
       <c r="R15" t="n">
-        <v>7003165</v>
+        <v>7003173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333827</v>
+        <v>123333819</v>
       </c>
       <c r="B16" t="n">
         <v>79869</v>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519272</v>
+        <v>519202</v>
       </c>
       <c r="R16" t="n">
-        <v>7003098</v>
+        <v>7003229</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333832</v>
+        <v>123333798</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519246</v>
+        <v>519233</v>
       </c>
       <c r="R17" t="n">
-        <v>7003145</v>
+        <v>7003181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333823</v>
+        <v>123333822</v>
       </c>
       <c r="B18" t="n">
         <v>79869</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519345</v>
+        <v>519337</v>
       </c>
       <c r="R18" t="n">
-        <v>7003129</v>
+        <v>7003139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333818</v>
+        <v>123333825</v>
       </c>
       <c r="B19" t="n">
         <v>79869</v>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519316</v>
+        <v>519351</v>
       </c>
       <c r="R19" t="n">
-        <v>7003189</v>
+        <v>7003097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,6 +2530,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333804</v>
+        <v>123333826</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519267</v>
+        <v>519347</v>
       </c>
       <c r="R20" t="n">
-        <v>7003104</v>
+        <v>7003094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,11 +2637,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,7 +2663,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333801</v>
+        <v>123333803</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519296</v>
+        <v>519276</v>
       </c>
       <c r="R21" t="n">
-        <v>7003116</v>
+        <v>7003096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333832</v>
+        <v>123333805</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519246</v>
+        <v>519254</v>
       </c>
       <c r="R7" t="n">
-        <v>7003145</v>
+        <v>7003096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333805</v>
+        <v>123333832</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519254</v>
+        <v>519246</v>
       </c>
       <c r="R8" t="n">
-        <v>7003096</v>
+        <v>7003145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333819</v>
+        <v>123333798</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519202</v>
+        <v>519233</v>
       </c>
       <c r="R16" t="n">
-        <v>7003229</v>
+        <v>7003181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2219,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333798</v>
+        <v>123333819</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519233</v>
+        <v>519202</v>
       </c>
       <c r="R17" t="n">
-        <v>7003181</v>
+        <v>7003229</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,11 +2326,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333801</v>
+        <v>123333817</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519296</v>
+        <v>519229</v>
       </c>
       <c r="R2" t="n">
-        <v>7003116</v>
+        <v>7003181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333824</v>
+        <v>123333826</v>
       </c>
       <c r="B3" t="n">
         <v>79869</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519360</v>
+        <v>519347</v>
       </c>
       <c r="R3" t="n">
-        <v>7003138</v>
+        <v>7003094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333823</v>
+        <v>123333824</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519345</v>
+        <v>519360</v>
       </c>
       <c r="R4" t="n">
-        <v>7003129</v>
+        <v>7003138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333818</v>
+        <v>123333805</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519316</v>
+        <v>519254</v>
       </c>
       <c r="R5" t="n">
-        <v>7003189</v>
+        <v>7003096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333799</v>
+        <v>123333804</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519233</v>
+        <v>519267</v>
       </c>
       <c r="R6" t="n">
-        <v>7003190</v>
+        <v>7003104</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333805</v>
+        <v>123333801</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519254</v>
+        <v>519296</v>
       </c>
       <c r="R7" t="n">
-        <v>7003096</v>
+        <v>7003116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333832</v>
+        <v>123333818</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519246</v>
+        <v>519316</v>
       </c>
       <c r="R8" t="n">
-        <v>7003145</v>
+        <v>7003189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333800</v>
+        <v>123333822</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519340</v>
+        <v>519337</v>
       </c>
       <c r="R9" t="n">
-        <v>7003134</v>
+        <v>7003139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333817</v>
+        <v>123333827</v>
       </c>
       <c r="B10" t="n">
         <v>79869</v>
@@ -1556,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519229</v>
+        <v>519272</v>
       </c>
       <c r="R10" t="n">
-        <v>7003181</v>
+        <v>7003098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333821</v>
+        <v>123333832</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519369</v>
+        <v>519246</v>
       </c>
       <c r="R11" t="n">
-        <v>7003165</v>
+        <v>7003145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333806</v>
+        <v>123333825</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519245</v>
+        <v>519351</v>
       </c>
       <c r="R12" t="n">
-        <v>7003107</v>
+        <v>7003097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333804</v>
+        <v>123333823</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519267</v>
+        <v>519345</v>
       </c>
       <c r="R13" t="n">
-        <v>7003104</v>
+        <v>7003129</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333827</v>
+        <v>123333799</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519272</v>
+        <v>519233</v>
       </c>
       <c r="R14" t="n">
-        <v>7003098</v>
+        <v>7003190</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333831</v>
+        <v>123333803</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519255</v>
+        <v>519276</v>
       </c>
       <c r="R15" t="n">
-        <v>7003173</v>
+        <v>7003096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2111,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333798</v>
+        <v>123333821</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519233</v>
+        <v>519369</v>
       </c>
       <c r="R16" t="n">
-        <v>7003181</v>
+        <v>7003165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333822</v>
+        <v>123333806</v>
       </c>
       <c r="B18" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519337</v>
+        <v>519245</v>
       </c>
       <c r="R18" t="n">
-        <v>7003139</v>
+        <v>7003107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2418,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333825</v>
+        <v>123333831</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519351</v>
+        <v>519255</v>
       </c>
       <c r="R19" t="n">
-        <v>7003097</v>
+        <v>7003173</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mycket rikligt på sälg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333826</v>
+        <v>123333800</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,21 +2572,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519347</v>
+        <v>519340</v>
       </c>
       <c r="R20" t="n">
-        <v>7003094</v>
+        <v>7003134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2632,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,7 +2663,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333803</v>
+        <v>123333798</v>
       </c>
       <c r="B21" t="n">
         <v>57491</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519276</v>
+        <v>519233</v>
       </c>
       <c r="R21" t="n">
-        <v>7003096</v>
+        <v>7003181</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333817</v>
+        <v>123333798</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519229</v>
+        <v>519233</v>
       </c>
       <c r="R2" t="n">
         <v>7003181</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333826</v>
+        <v>123333799</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519347</v>
+        <v>519233</v>
       </c>
       <c r="R3" t="n">
-        <v>7003094</v>
+        <v>7003190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333824</v>
+        <v>123333803</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519360</v>
+        <v>519276</v>
       </c>
       <c r="R4" t="n">
-        <v>7003138</v>
+        <v>7003096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333805</v>
+        <v>123333818</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519254</v>
+        <v>519316</v>
       </c>
       <c r="R5" t="n">
-        <v>7003096</v>
+        <v>7003189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333804</v>
+        <v>123333826</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519267</v>
+        <v>519347</v>
       </c>
       <c r="R6" t="n">
-        <v>7003104</v>
+        <v>7003094</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333801</v>
+        <v>123333825</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519296</v>
+        <v>519351</v>
       </c>
       <c r="R7" t="n">
-        <v>7003116</v>
+        <v>7003097</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333818</v>
+        <v>123333817</v>
       </c>
       <c r="B8" t="n">
         <v>79869</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519316</v>
+        <v>519229</v>
       </c>
       <c r="R8" t="n">
-        <v>7003189</v>
+        <v>7003181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333822</v>
+        <v>123333806</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519337</v>
+        <v>519245</v>
       </c>
       <c r="R9" t="n">
-        <v>7003139</v>
+        <v>7003107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333827</v>
+        <v>123333832</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519272</v>
+        <v>519246</v>
       </c>
       <c r="R10" t="n">
-        <v>7003098</v>
+        <v>7003145</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333832</v>
+        <v>123333804</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519246</v>
+        <v>519267</v>
       </c>
       <c r="R11" t="n">
-        <v>7003145</v>
+        <v>7003104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333825</v>
+        <v>123333822</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1755,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519351</v>
+        <v>519337</v>
       </c>
       <c r="R12" t="n">
-        <v>7003097</v>
+        <v>7003139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333823</v>
+        <v>123333819</v>
       </c>
       <c r="B13" t="n">
         <v>79869</v>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519345</v>
+        <v>519202</v>
       </c>
       <c r="R13" t="n">
-        <v>7003129</v>
+        <v>7003229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333799</v>
+        <v>123333823</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519233</v>
+        <v>519345</v>
       </c>
       <c r="R14" t="n">
-        <v>7003190</v>
+        <v>7003129</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333803</v>
+        <v>123333831</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519276</v>
+        <v>519255</v>
       </c>
       <c r="R15" t="n">
-        <v>7003096</v>
+        <v>7003173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,7 +2116,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333821</v>
+        <v>123333800</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519369</v>
+        <v>519340</v>
       </c>
       <c r="R16" t="n">
-        <v>7003165</v>
+        <v>7003134</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2219,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333819</v>
+        <v>123333801</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519202</v>
+        <v>519296</v>
       </c>
       <c r="R17" t="n">
-        <v>7003229</v>
+        <v>7003116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2326,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333806</v>
+        <v>123333805</v>
       </c>
       <c r="B18" t="n">
         <v>57491</v>
@@ -2382,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519245</v>
+        <v>519254</v>
       </c>
       <c r="R18" t="n">
-        <v>7003107</v>
+        <v>7003096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333831</v>
+        <v>123333827</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519255</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7003173</v>
+        <v>7003098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333800</v>
+        <v>123333821</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519340</v>
+        <v>519369</v>
       </c>
       <c r="R20" t="n">
-        <v>7003134</v>
+        <v>7003165</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,11 +2642,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333798</v>
+        <v>123333824</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519233</v>
+        <v>519360</v>
       </c>
       <c r="R21" t="n">
-        <v>7003181</v>
+        <v>7003138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333798</v>
+        <v>123333806</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519233</v>
+        <v>519245</v>
       </c>
       <c r="R2" t="n">
-        <v>7003181</v>
+        <v>7003107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333803</v>
+        <v>123333805</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519276</v>
+        <v>519254</v>
       </c>
       <c r="R4" t="n">
         <v>7003096</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333818</v>
+        <v>123333822</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519316</v>
+        <v>519337</v>
       </c>
       <c r="R5" t="n">
-        <v>7003189</v>
+        <v>7003139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333826</v>
+        <v>123333825</v>
       </c>
       <c r="B6" t="n">
         <v>79869</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519347</v>
+        <v>519351</v>
       </c>
       <c r="R6" t="n">
-        <v>7003094</v>
+        <v>7003097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333825</v>
+        <v>123333818</v>
       </c>
       <c r="B7" t="n">
         <v>79869</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519351</v>
+        <v>519316</v>
       </c>
       <c r="R7" t="n">
-        <v>7003097</v>
+        <v>7003189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333817</v>
+        <v>123333803</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519229</v>
+        <v>519276</v>
       </c>
       <c r="R8" t="n">
-        <v>7003181</v>
+        <v>7003096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333806</v>
+        <v>123333827</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519245</v>
+        <v>519272</v>
       </c>
       <c r="R9" t="n">
-        <v>7003107</v>
+        <v>7003098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333832</v>
+        <v>123333824</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519246</v>
+        <v>519360</v>
       </c>
       <c r="R10" t="n">
-        <v>7003145</v>
+        <v>7003138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333804</v>
+        <v>123333821</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519267</v>
+        <v>519369</v>
       </c>
       <c r="R11" t="n">
-        <v>7003104</v>
+        <v>7003165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333822</v>
+        <v>123333832</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519337</v>
+        <v>519246</v>
       </c>
       <c r="R12" t="n">
-        <v>7003139</v>
+        <v>7003145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333819</v>
+        <v>123333804</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519202</v>
+        <v>519267</v>
       </c>
       <c r="R13" t="n">
-        <v>7003229</v>
+        <v>7003104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333823</v>
+        <v>123333798</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519345</v>
+        <v>519233</v>
       </c>
       <c r="R14" t="n">
-        <v>7003129</v>
+        <v>7003181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333831</v>
+        <v>123333819</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519255</v>
+        <v>519202</v>
       </c>
       <c r="R15" t="n">
-        <v>7003173</v>
+        <v>7003229</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333801</v>
+        <v>123333831</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519296</v>
+        <v>519255</v>
       </c>
       <c r="R17" t="n">
-        <v>7003116</v>
+        <v>7003173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333805</v>
+        <v>123333801</v>
       </c>
       <c r="B18" t="n">
         <v>57491</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519254</v>
+        <v>519296</v>
       </c>
       <c r="R18" t="n">
-        <v>7003096</v>
+        <v>7003116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333827</v>
+        <v>123333817</v>
       </c>
       <c r="B19" t="n">
         <v>79869</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519229</v>
       </c>
       <c r="R19" t="n">
-        <v>7003098</v>
+        <v>7003181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333821</v>
+        <v>123333826</v>
       </c>
       <c r="B20" t="n">
         <v>79869</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519369</v>
+        <v>519347</v>
       </c>
       <c r="R20" t="n">
-        <v>7003165</v>
+        <v>7003094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333824</v>
+        <v>123333823</v>
       </c>
       <c r="B21" t="n">
         <v>79869</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519360</v>
+        <v>519345</v>
       </c>
       <c r="R21" t="n">
-        <v>7003138</v>
+        <v>7003129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333824</v>
+        <v>123333804</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519360</v>
+        <v>519267</v>
       </c>
       <c r="R10" t="n">
-        <v>7003138</v>
+        <v>7003104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333821</v>
+        <v>123333798</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519369</v>
+        <v>519233</v>
       </c>
       <c r="R11" t="n">
-        <v>7003165</v>
+        <v>7003181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333832</v>
+        <v>123333824</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519246</v>
+        <v>519360</v>
       </c>
       <c r="R12" t="n">
-        <v>7003145</v>
+        <v>7003138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333804</v>
+        <v>123333821</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519267</v>
+        <v>519369</v>
       </c>
       <c r="R13" t="n">
-        <v>7003104</v>
+        <v>7003165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333798</v>
+        <v>123333832</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519233</v>
+        <v>519246</v>
       </c>
       <c r="R14" t="n">
-        <v>7003181</v>
+        <v>7003145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333806</v>
+        <v>123333824</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519245</v>
+        <v>519360</v>
       </c>
       <c r="R2" t="n">
-        <v>7003107</v>
+        <v>7003138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333799</v>
+        <v>123333801</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519233</v>
+        <v>519296</v>
       </c>
       <c r="R3" t="n">
-        <v>7003190</v>
+        <v>7003116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333805</v>
+        <v>123333804</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519254</v>
+        <v>519267</v>
       </c>
       <c r="R4" t="n">
-        <v>7003096</v>
+        <v>7003104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333822</v>
+        <v>123333821</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519337</v>
+        <v>519369</v>
       </c>
       <c r="R5" t="n">
-        <v>7003139</v>
+        <v>7003165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333818</v>
+        <v>123333805</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519316</v>
+        <v>519254</v>
       </c>
       <c r="R7" t="n">
-        <v>7003189</v>
+        <v>7003096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333803</v>
+        <v>123333832</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519276</v>
+        <v>519246</v>
       </c>
       <c r="R8" t="n">
-        <v>7003096</v>
+        <v>7003145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333827</v>
+        <v>123333798</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519272</v>
+        <v>519233</v>
       </c>
       <c r="R9" t="n">
-        <v>7003098</v>
+        <v>7003181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333804</v>
+        <v>123333826</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519267</v>
+        <v>519347</v>
       </c>
       <c r="R10" t="n">
-        <v>7003104</v>
+        <v>7003094</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333798</v>
+        <v>123333823</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519233</v>
+        <v>519345</v>
       </c>
       <c r="R11" t="n">
-        <v>7003181</v>
+        <v>7003129</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333824</v>
+        <v>123333818</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519360</v>
+        <v>519316</v>
       </c>
       <c r="R12" t="n">
-        <v>7003138</v>
+        <v>7003189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333821</v>
+        <v>123333831</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519369</v>
+        <v>519255</v>
       </c>
       <c r="R13" t="n">
-        <v>7003165</v>
+        <v>7003173</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333832</v>
+        <v>123333822</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519246</v>
+        <v>519337</v>
       </c>
       <c r="R14" t="n">
-        <v>7003145</v>
+        <v>7003139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333819</v>
+        <v>123333806</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519202</v>
+        <v>519245</v>
       </c>
       <c r="R15" t="n">
-        <v>7003229</v>
+        <v>7003107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333800</v>
+        <v>123333819</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519340</v>
+        <v>519202</v>
       </c>
       <c r="R16" t="n">
-        <v>7003134</v>
+        <v>7003229</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333831</v>
+        <v>123333817</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519255</v>
+        <v>519229</v>
       </c>
       <c r="R17" t="n">
-        <v>7003173</v>
+        <v>7003181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2321,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2347,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123333801</v>
+        <v>123333800</v>
       </c>
       <c r="B18" t="n">
         <v>57491</v>
@@ -2397,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519296</v>
+        <v>519340</v>
       </c>
       <c r="R18" t="n">
-        <v>7003116</v>
+        <v>7003134</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2454,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333817</v>
+        <v>123333827</v>
       </c>
       <c r="B19" t="n">
         <v>79869</v>
@@ -2504,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519229</v>
+        <v>519272</v>
       </c>
       <c r="R19" t="n">
-        <v>7003181</v>
+        <v>7003098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333826</v>
+        <v>123333799</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2572,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519347</v>
+        <v>519233</v>
       </c>
       <c r="R20" t="n">
-        <v>7003094</v>
+        <v>7003190</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,6 +2632,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333823</v>
+        <v>123333803</v>
       </c>
       <c r="B21" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519345</v>
+        <v>519276</v>
       </c>
       <c r="R21" t="n">
-        <v>7003129</v>
+        <v>7003096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2739,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333824</v>
+        <v>123333816</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519360</v>
+        <v>519214</v>
       </c>
       <c r="R2" t="n">
-        <v>7003138</v>
+        <v>7003094</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333801</v>
+        <v>123333797</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519296</v>
+        <v>519213</v>
       </c>
       <c r="R3" t="n">
-        <v>7003116</v>
+        <v>7003094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333804</v>
+        <v>123333831</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519267</v>
+        <v>519255</v>
       </c>
       <c r="R4" t="n">
-        <v>7003104</v>
+        <v>7003173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333821</v>
+        <v>123333832</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519369</v>
+        <v>519246</v>
       </c>
       <c r="R5" t="n">
-        <v>7003165</v>
+        <v>7003145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333825</v>
+        <v>123333817</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519351</v>
+        <v>519229</v>
       </c>
       <c r="R6" t="n">
-        <v>7003097</v>
+        <v>7003181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333805</v>
+        <v>123333818</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519254</v>
+        <v>519316</v>
       </c>
       <c r="R7" t="n">
-        <v>7003096</v>
+        <v>7003189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333832</v>
+        <v>123333819</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519246</v>
+        <v>519202</v>
       </c>
       <c r="R8" t="n">
-        <v>7003145</v>
+        <v>7003229</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333798</v>
+        <v>123333821</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519233</v>
+        <v>519369</v>
       </c>
       <c r="R9" t="n">
-        <v>7003181</v>
+        <v>7003165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333826</v>
+        <v>123333822</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519347</v>
+        <v>519337</v>
       </c>
       <c r="R10" t="n">
-        <v>7003094</v>
+        <v>7003139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,12 +1561,7 @@
         <v>123333823</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333818</v>
+        <v>123333824</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519316</v>
+        <v>519360</v>
       </c>
       <c r="R12" t="n">
-        <v>7003189</v>
+        <v>7003138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333831</v>
+        <v>123333825</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519255</v>
+        <v>519351</v>
       </c>
       <c r="R13" t="n">
-        <v>7003173</v>
+        <v>7003097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1827,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333822</v>
+        <v>123333826</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519337</v>
+        <v>519347</v>
       </c>
       <c r="R14" t="n">
-        <v>7003139</v>
+        <v>7003094</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,15 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333806</v>
+        <v>123333827</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519245</v>
+        <v>519272</v>
       </c>
       <c r="R15" t="n">
-        <v>7003107</v>
+        <v>7003098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,15 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333819</v>
+        <v>123333798</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519202</v>
+        <v>519233</v>
       </c>
       <c r="R16" t="n">
-        <v>7003229</v>
+        <v>7003181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,15 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333817</v>
+        <v>123333799</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519229</v>
+        <v>519233</v>
       </c>
       <c r="R17" t="n">
-        <v>7003181</v>
+        <v>7003190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,6 +2221,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,12 +2255,7 @@
         <v>123333800</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,15 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123333827</v>
+        <v>123333801</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519272</v>
+        <v>519296</v>
       </c>
       <c r="R19" t="n">
-        <v>7003098</v>
+        <v>7003116</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,6 +2425,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,15 +2456,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123333799</v>
+        <v>123333803</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519233</v>
+        <v>519276</v>
       </c>
       <c r="R20" t="n">
-        <v>7003190</v>
+        <v>7003096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,15 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123333803</v>
+        <v>123333804</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519276</v>
+        <v>519267</v>
       </c>
       <c r="R21" t="n">
-        <v>7003096</v>
+        <v>7003104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,7 +2633,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2767,6 +2657,312 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123333805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lillsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>519254</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7003096</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123333806</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>519245</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7003107</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123333807</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>519217</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7003090</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57941-2024 artfynd.xlsx
+++ b/artfynd/A 57941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333816</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333797</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333818</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333819</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333822</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333824</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333825</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333826</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333827</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333799</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333800</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333801</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333803</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333804</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333805</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2764,6 +2869,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333806</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333807</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,8 +3078,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>